--- a/data-raw/desc_IAG.xlsx
+++ b/data-raw/desc_IAG.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29301"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\2.Programação e Normas\2023\PPAG 2023 e LOA 2023\Tabelas de Apoio - geração dos volumes 2023\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cecad365.sharepoint.com/sites/Splor/Documentos Compartilhados/General/@dcppn/00- DCPPN 2027/PPAG e LOA 2027/Dados para Volumes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_E3980003A353832A5484981D7F934B739E91CF99" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7020"/>
   </bookViews>
   <sheets>
     <sheet name="Identificador de ação govername" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
   <definedNames>
     <definedName name="LOCAL_MYSQL_DATE_FORMAT" hidden="1">REPT(LOCAL_YEAR_FORMAT,4)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_MONTH_FORMAT,2)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_DAY_FORMAT,2)&amp;" "&amp;REPT(LOCAL_HOUR_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_MINUTE_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_SECOND_FORMAT,2)</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -50,14 +49,14 @@
     <t>Demais Projetos e Atividades</t>
   </si>
   <si>
-    <t>Projeto Estratégico</t>
+    <t>Projetos Estratégicos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,15 +366,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -383,7 +382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -391,7 +390,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -405,15 +404,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
@@ -431,9 +421,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7797dc5feb179b4da55a9ebddd321181">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90078f443198b6d5c0fd169535a443b9" ns2:_="" ns3:_="">
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="b1e0f6055e0e9a4b9e75d6c71ee7de91">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b43930f3490e4d4da1ab3f8da7df6f51" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
     <xsd:import namespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
     <xsd:element name="properties">
@@ -692,14 +682,55 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BC130D8-0701-40A9-879C-A96F98BAA011}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4E4BBAB-28ED-4CB1-8E29-525636D93572}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4E4BBAB-28ED-4CB1-8E29-525636D93572}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EEBEC4A-35C8-47CC-A833-EAA3800F06E2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{919EDD7F-C933-4F35-9E7B-22FE561B3FB0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BC130D8-0701-40A9-879C-A96F98BAA011}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>